--- a/exports/trend_1d/FEDERALBNK_full_report.xlsx
+++ b/exports/trend_1d/FEDERALBNK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42039</v>
+        <v>42040</v>
       </c>
       <c r="H2" t="n">
-        <v>70.05</v>
+        <v>68.5</v>
       </c>
       <c r="I2" t="n">
         <v>69.32499999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.11</v>
+        <v>-5.26</v>
       </c>
       <c r="L2" t="n">
-        <v>3.53</v>
+        <v>7.95</v>
       </c>
       <c r="M2" t="n">
         <v>0.14</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42063</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>71.34999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="I3" t="n">
         <v>74.2178303728284</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.16</v>
+        <v>-9.56</v>
       </c>
       <c r="L3" t="n">
-        <v>6.06</v>
+        <v>10.51</v>
       </c>
       <c r="M3" t="n">
         <v>2.31</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>5.19</v>
       </c>
       <c r="O3" t="n">
         <v>-2.21</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.72</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H4" t="n">
-        <v>69.8</v>
+        <v>68</v>
       </c>
       <c r="I4" t="n">
         <v>68.51453629258708</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>-7</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>9.130000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>1.5</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.62</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42124</v>
+        <v>42128</v>
       </c>
       <c r="H5" t="n">
-        <v>65.7</v>
+        <v>68.25</v>
       </c>
       <c r="I5" t="n">
         <v>67.47840388069642</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K5" t="n">
-        <v>3.38</v>
+        <v>-0.37</v>
       </c>
       <c r="L5" t="n">
         <v>4.85</v>
@@ -726,7 +785,7 @@
         <v>1.44</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="O5" t="n">
         <v>-2.58</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.77</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42202</v>
+        <v>42205</v>
       </c>
       <c r="H6" t="n">
-        <v>75.8</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
         <v>71.04545553996581</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K6" t="n">
-        <v>11.06</v>
+        <v>3.59</v>
       </c>
       <c r="L6" t="n">
         <v>8.789999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>3.66</v>
+        <v>6.33</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>6.73</v>
       </c>
       <c r="O6" t="n">
         <v>3.88</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H7" t="n">
-        <v>63.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>64.38731436156044</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>10.61</v>
+        <v>7.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.56</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>12.18</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42297</v>
+        <v>42298</v>
       </c>
       <c r="H8" t="n">
-        <v>65.45</v>
+        <v>57.45</v>
       </c>
       <c r="I8" t="n">
         <v>60.6180641246721</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>-12.16</v>
       </c>
       <c r="L8" t="n">
-        <v>4.74</v>
+        <v>14.76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.73</v>
+        <v>7.56</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>12.22</v>
       </c>
       <c r="O8" t="n">
         <v>3.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.79</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42419</v>
+        <v>42422</v>
       </c>
       <c r="H9" t="n">
-        <v>48.3</v>
+        <v>49.35</v>
       </c>
       <c r="I9" t="n">
         <v>48.72931925450487</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K9" t="n">
-        <v>15.93</v>
+        <v>14.1</v>
       </c>
       <c r="L9" t="n">
         <v>6.18</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>13.27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42464</v>
+        <v>42465</v>
       </c>
       <c r="H10" t="n">
-        <v>44.85</v>
+        <v>43.65</v>
       </c>
       <c r="I10" t="n">
         <v>44.79982690233927</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.119999999999999</v>
+        <v>-11.55</v>
       </c>
       <c r="L10" t="n">
-        <v>10.84</v>
+        <v>12.06</v>
       </c>
       <c r="M10" t="n">
         <v>2.71</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>14.84</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42482</v>
+        <v>42485</v>
       </c>
       <c r="H11" t="n">
-        <v>47.4</v>
+        <v>48.15</v>
       </c>
       <c r="I11" t="n">
         <v>48.00456258782885</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.59</v>
+        <v>-10.31</v>
       </c>
       <c r="L11" t="n">
-        <v>10.08</v>
+        <v>11.57</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.71</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H12" t="n">
-        <v>77.3</v>
+        <v>73.8</v>
       </c>
       <c r="I12" t="n">
         <v>73.96767221276274</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K12" t="n">
-        <v>60.54</v>
+        <v>53.27</v>
       </c>
       <c r="L12" t="n">
         <v>9.35</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>17.89</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H13" t="n">
-        <v>69.90000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="I13" t="n">
         <v>70.08777572597344</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>5.28</v>
+        <v>1.69</v>
       </c>
       <c r="L13" t="n">
         <v>6.37</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H14" t="n">
-        <v>112.3</v>
+        <v>108.3</v>
       </c>
       <c r="I14" t="n">
         <v>110.6025404197663</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K14" t="n">
-        <v>54.79</v>
+        <v>49.28</v>
       </c>
       <c r="L14" t="n">
         <v>3.39</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.29</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42992</v>
+        <v>42993</v>
       </c>
       <c r="H15" t="n">
-        <v>114.55</v>
+        <v>115.45</v>
       </c>
       <c r="I15" t="n">
         <v>114.7734797722892</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.77</v>
+        <v>-6.6</v>
       </c>
       <c r="L15" t="n">
-        <v>6.19</v>
+        <v>7.02</v>
       </c>
       <c r="M15" t="n">
         <v>1.39</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.45</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H16" t="n">
-        <v>113.85</v>
+        <v>111.35</v>
       </c>
       <c r="I16" t="n">
         <v>112.369757399845</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.39</v>
+        <v>-3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>4.29</v>
       </c>
       <c r="M16" t="n">
         <v>0.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.08</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H17" t="n">
-        <v>117.2</v>
+        <v>124.8</v>
       </c>
       <c r="I17" t="n">
         <v>119.4769321699617</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.25</v>
+        <v>-12.08</v>
       </c>
       <c r="L17" t="n">
-        <v>7.72</v>
+        <v>12.44</v>
       </c>
       <c r="M17" t="n">
         <v>0.89</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>6.48</v>
       </c>
       <c r="O17" t="n">
         <v>-2.2</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>11.3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43041</v>
+        <v>43042</v>
       </c>
       <c r="H18" t="n">
-        <v>118.15</v>
+        <v>115.9</v>
       </c>
       <c r="I18" t="n">
         <v>117.1966731424524</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.33</v>
+        <v>-7.13</v>
       </c>
       <c r="L18" t="n">
-        <v>7.13</v>
+        <v>7.53</v>
       </c>
       <c r="M18" t="n">
         <v>0.62</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.12</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H19" t="n">
-        <v>112.1</v>
+        <v>115.55</v>
       </c>
       <c r="I19" t="n">
         <v>112.3820413091193</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K19" t="n">
-        <v>3.28</v>
+        <v>0.3</v>
       </c>
       <c r="L19" t="n">
         <v>3.02</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H20" t="n">
-        <v>113.6</v>
+        <v>104.75</v>
       </c>
       <c r="I20" t="n">
         <v>106.653448302036</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.69</v>
+        <v>-9.35</v>
       </c>
       <c r="L20" t="n">
-        <v>5.11</v>
+        <v>9.91</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="N20" t="n">
-        <v>1.74</v>
+        <v>7.79</v>
       </c>
       <c r="O20" t="n">
         <v>3.08</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.86</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H21" t="n">
-        <v>93.5</v>
+        <v>97.25</v>
       </c>
       <c r="I21" t="n">
         <v>97.15458483990609</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" t="n">
-        <v>10.74</v>
+        <v>7.16</v>
       </c>
       <c r="L21" t="n">
         <v>7.11</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H22" t="n">
-        <v>101.15</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>94.65955335592233</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>4.01</v>
+        <v>-8.07</v>
       </c>
       <c r="L22" t="n">
-        <v>4.88</v>
+        <v>9.41</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4</v>
+        <v>7.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.22</v>
+        <v>11.62</v>
       </c>
       <c r="O22" t="n">
         <v>4.01</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43297</v>
+        <v>43298</v>
       </c>
       <c r="H23" t="n">
-        <v>74.15000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="I23" t="n">
         <v>85.23536375528074</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K23" t="n">
-        <v>17.06</v>
+        <v>1.23</v>
       </c>
       <c r="L23" t="n">
         <v>4.59</v>
@@ -1752,7 +2027,7 @@
         <v>6.79</v>
       </c>
       <c r="N23" t="n">
-        <v>4.14</v>
+        <v>19.08</v>
       </c>
       <c r="O23" t="n">
         <v>-11.62</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>22.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43329</v>
+        <v>43332</v>
       </c>
       <c r="H24" t="n">
-        <v>86.25</v>
+        <v>81.5</v>
       </c>
       <c r="I24" t="n">
         <v>81.53813489323213</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.32</v>
+        <v>-7.7</v>
       </c>
       <c r="L24" t="n">
         <v>16.76</v>
@@ -1809,7 +2096,7 @@
         <v>1.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>5.51</v>
       </c>
       <c r="O24" t="n">
         <v>19.08</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43388</v>
+        <v>43389</v>
       </c>
       <c r="H25" t="n">
-        <v>75.8</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>77.51381285943381</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>6.99</v>
+        <v>-0.18</v>
       </c>
       <c r="L25" t="n">
         <v>5.89</v>
@@ -1866,7 +2165,7 @@
         <v>1.96</v>
       </c>
       <c r="N25" t="n">
-        <v>4.01</v>
+        <v>7.72</v>
       </c>
       <c r="O25" t="n">
         <v>-5.51</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>15.3</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H26" t="n">
-        <v>88.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I26" t="n">
         <v>88.25440758691238</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K26" t="n">
-        <v>8.880000000000001</v>
+        <v>5.94</v>
       </c>
       <c r="L26" t="n">
         <v>6.5</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.95</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H27" t="n">
-        <v>83.84999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I27" t="n">
         <v>85.46296128226284</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.06</v>
+        <v>0.92</v>
       </c>
       <c r="L27" t="n">
         <v>3.29</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H28" t="n">
-        <v>103.15</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>101.9124664220194</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K28" t="n">
-        <v>20.36</v>
+        <v>15.69</v>
       </c>
       <c r="L28" t="n">
         <v>2.45</v>
@@ -2037,7 +2372,7 @@
         <v>1.26</v>
       </c>
       <c r="N28" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="O28" t="n">
         <v>2.21</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.37</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H29" t="n">
-        <v>83.45</v>
+        <v>94.8</v>
       </c>
       <c r="I29" t="n">
         <v>89.97043534881678</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K29" t="n">
-        <v>15.83</v>
+        <v>4.39</v>
       </c>
       <c r="L29" t="n">
         <v>4.24</v>
@@ -2094,7 +2441,7 @@
         <v>2.85</v>
       </c>
       <c r="N29" t="n">
-        <v>3.73</v>
+        <v>13.6</v>
       </c>
       <c r="O29" t="n">
         <v>-3.88</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>17.3</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43749</v>
+        <v>43752</v>
       </c>
       <c r="H30" t="n">
-        <v>84.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="I30" t="n">
         <v>83.66306147004602</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.23</v>
+        <v>-12.18</v>
       </c>
       <c r="L30" t="n">
         <v>15.61</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.34</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43796</v>
+        <v>43797</v>
       </c>
       <c r="H31" t="n">
-        <v>87.45</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>90.42811290179394</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.05</v>
+        <v>-9.19</v>
       </c>
       <c r="L31" t="n">
         <v>10.63</v>
@@ -2208,7 +2579,7 @@
         <v>1.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="O31" t="n">
         <v>-1.07</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.73</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43874</v>
+        <v>43875</v>
       </c>
       <c r="H32" t="n">
-        <v>89.2</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>88.03716930853651</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.87</v>
+        <v>-4.13</v>
       </c>
       <c r="L32" t="n">
         <v>8.69</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.69</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H33" t="n">
-        <v>44.9</v>
+        <v>46.65</v>
       </c>
       <c r="I33" t="n">
         <v>46.0205770118226</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K33" t="n">
-        <v>48.48</v>
+        <v>46.47</v>
       </c>
       <c r="L33" t="n">
         <v>3.21</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>18.38</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H34" t="n">
-        <v>53.85</v>
+        <v>52.85</v>
       </c>
       <c r="I34" t="n">
         <v>53.116829805035</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K34" t="n">
-        <v>15.43</v>
+        <v>13.29</v>
       </c>
       <c r="L34" t="n">
         <v>5.57</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.92</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44120</v>
+        <v>44123</v>
       </c>
       <c r="H35" t="n">
-        <v>52.2</v>
+        <v>56.2</v>
       </c>
       <c r="I35" t="n">
         <v>53.51396191582093</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K35" t="n">
-        <v>1.23</v>
+        <v>-6.34</v>
       </c>
       <c r="L35" t="n">
-        <v>4.07</v>
+        <v>7.1</v>
       </c>
       <c r="M35" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="N35" t="n">
-        <v>5.87</v>
+        <v>7.66</v>
       </c>
       <c r="O35" t="n">
         <v>-1.86</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>13.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44133</v>
+        <v>44134</v>
       </c>
       <c r="H36" t="n">
-        <v>51</v>
+        <v>50.45</v>
       </c>
       <c r="I36" t="n">
         <v>50.49479223709761</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.25</v>
+        <v>-10.23</v>
       </c>
       <c r="L36" t="n">
-        <v>10.59</v>
+        <v>11.39</v>
       </c>
       <c r="M36" t="n">
         <v>1.16</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>12.3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H37" t="n">
-        <v>55.7</v>
+        <v>58.65</v>
       </c>
       <c r="I37" t="n">
         <v>56.65465547935214</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.41</v>
+        <v>-16.25</v>
       </c>
       <c r="L37" t="n">
-        <v>12.09</v>
+        <v>16.95</v>
       </c>
       <c r="M37" t="n">
         <v>1.37</v>
       </c>
       <c r="N37" t="n">
-        <v>3.58</v>
+        <v>5.3</v>
       </c>
       <c r="O37" t="n">
         <v>-1.08</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.81</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H38" t="n">
-        <v>66.34</v>
+        <v>60.4</v>
       </c>
       <c r="I38" t="n">
         <v>61.55018649223345</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>13.11</v>
+        <v>2.98</v>
       </c>
       <c r="L38" t="n">
         <v>6.73</v>
@@ -2607,7 +3062,7 @@
         <v>0.89</v>
       </c>
       <c r="N38" t="n">
-        <v>5.33</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O38" t="n">
         <v>5.3</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>16.96</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H39" t="n">
-        <v>68.05</v>
+        <v>70.55</v>
       </c>
       <c r="I39" t="n">
         <v>68.33331404716182</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.67</v>
+        <v>-16.8</v>
       </c>
       <c r="L39" t="n">
-        <v>13</v>
+        <v>18.21</v>
       </c>
       <c r="M39" t="n">
-        <v>0.98</v>
+        <v>1.4</v>
       </c>
       <c r="N39" t="n">
         <v>3.96</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.92</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H40" t="n">
-        <v>80.2</v>
+        <v>77.75</v>
       </c>
       <c r="I40" t="n">
         <v>77.93791869312777</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K40" t="n">
-        <v>13.68</v>
+        <v>10.21</v>
       </c>
       <c r="L40" t="n">
         <v>2.48</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>16.82</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H41" t="n">
-        <v>81.55</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>82.21544295218783</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.89</v>
+        <v>-8.49</v>
       </c>
       <c r="L41" t="n">
-        <v>8.039999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="M41" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
         <v>8.15</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>12.99</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H42" t="n">
-        <v>83.25</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>83.05764469348617</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.3</v>
+        <v>-5.28</v>
       </c>
       <c r="L42" t="n">
-        <v>3.68</v>
+        <v>5.69</v>
       </c>
       <c r="M42" t="n">
         <v>1.59</v>
       </c>
       <c r="N42" t="n">
-        <v>2.62</v>
+        <v>4.02</v>
       </c>
       <c r="O42" t="n">
         <v>3.43</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.74</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H43" t="n">
-        <v>83.65000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>84.28143587348222</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.69</v>
+        <v>-7.51</v>
       </c>
       <c r="L43" t="n">
-        <v>5.69</v>
+        <v>7.88</v>
       </c>
       <c r="M43" t="n">
         <v>1.22</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H44" t="n">
-        <v>94.7</v>
+        <v>91.45</v>
       </c>
       <c r="I44" t="n">
         <v>91.46143078591768</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K44" t="n">
-        <v>10.24</v>
+        <v>6.46</v>
       </c>
       <c r="L44" t="n">
         <v>9.02</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H45" t="n">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="I45" t="n">
         <v>88.27446835214172</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>4.65</v>
+        <v>3.23</v>
       </c>
       <c r="L45" t="n">
         <v>4.21</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>93.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I46" t="n">
         <v>92.17144699654857</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>6.1</v>
+        <v>3.95</v>
       </c>
       <c r="L46" t="n">
         <v>1.81</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H47" t="n">
-        <v>100.25</v>
+        <v>101.4</v>
       </c>
       <c r="I47" t="n">
         <v>101.280614763008</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.970000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="L47" t="n">
         <v>11.68</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>9.92</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H48" t="n">
-        <v>100.3</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>94.32591689600042</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.08</v>
+        <v>-7.45</v>
       </c>
       <c r="L48" t="n">
-        <v>6.9</v>
+        <v>8.68</v>
       </c>
       <c r="M48" t="n">
-        <v>2.87</v>
+        <v>3.29</v>
       </c>
       <c r="N48" t="n">
         <v>6.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>14.02</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H49" t="n">
-        <v>97.40000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="I49" t="n">
         <v>99.99463119479681</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.78</v>
+        <v>-8.26</v>
       </c>
       <c r="L49" t="n">
-        <v>6.87</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>2.97</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>10.34</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H50" t="n">
-        <v>94.15000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I50" t="n">
         <v>94.05734417818195</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.33</v>
+        <v>-10.33</v>
       </c>
       <c r="L50" t="n">
-        <v>7.97</v>
+        <v>12.75</v>
       </c>
       <c r="M50" t="n">
         <v>2.08</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H51" t="n">
-        <v>90.2</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>92.79097554375912</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K51" t="n">
-        <v>0.99</v>
+        <v>-2.8</v>
       </c>
       <c r="L51" t="n">
         <v>4.28</v>
@@ -3348,7 +3959,7 @@
         <v>2.81</v>
       </c>
       <c r="N51" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="O51" t="n">
         <v>-3.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.88</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H52" t="n">
-        <v>116.75</v>
+        <v>111</v>
       </c>
       <c r="I52" t="n">
         <v>112.9014608233708</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K52" t="n">
-        <v>24.67</v>
+        <v>18.53</v>
       </c>
       <c r="L52" t="n">
         <v>4.64</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>13.15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44845</v>
+        <v>44846</v>
       </c>
       <c r="H53" t="n">
-        <v>122.4</v>
+        <v>125.6</v>
       </c>
       <c r="I53" t="n">
         <v>125.1356299402103</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K53" t="n">
-        <v>-10.27</v>
+        <v>-13.15</v>
       </c>
       <c r="L53" t="n">
-        <v>11.89</v>
+        <v>13.42</v>
       </c>
       <c r="M53" t="n">
         <v>2.15</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.2</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H54" t="n">
-        <v>130.9</v>
+        <v>127.95</v>
       </c>
       <c r="I54" t="n">
         <v>128.5392909837974</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K54" t="n">
-        <v>4.22</v>
+        <v>1.87</v>
       </c>
       <c r="L54" t="n">
         <v>3.03</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44923</v>
+        <v>44924</v>
       </c>
       <c r="H55" t="n">
-        <v>133.65</v>
+        <v>137.65</v>
       </c>
       <c r="I55" t="n">
         <v>137.0045861852797</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.45</v>
+        <v>-7.58</v>
       </c>
       <c r="L55" t="n">
-        <v>4.92</v>
+        <v>9.34</v>
       </c>
       <c r="M55" t="n">
         <v>0.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>12.06</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44973</v>
+        <v>44974</v>
       </c>
       <c r="H56" t="n">
-        <v>130.25</v>
+        <v>127.1</v>
       </c>
       <c r="I56" t="n">
         <v>128.0376296507077</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.38</v>
+        <v>-7.66</v>
       </c>
       <c r="L56" t="n">
-        <v>7.66</v>
+        <v>7.95</v>
       </c>
       <c r="M56" t="n">
         <v>2.55</v>
       </c>
       <c r="N56" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="O56" t="n">
         <v>2.99</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H57" t="n">
-        <v>134.15</v>
+        <v>135.9</v>
       </c>
       <c r="I57" t="n">
         <v>135.4281901396388</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.55</v>
+        <v>-6.92</v>
       </c>
       <c r="L57" t="n">
-        <v>6.96</v>
+        <v>7.2</v>
       </c>
       <c r="M57" t="n">
         <v>0.89</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H58" t="n">
-        <v>126.85</v>
+        <v>125.45</v>
       </c>
       <c r="I58" t="n">
         <v>126.048087210592</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.66</v>
+        <v>-7.69</v>
       </c>
       <c r="L58" t="n">
         <v>8.35</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.15</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45040</v>
+        <v>45041</v>
       </c>
       <c r="H59" t="n">
-        <v>132.1</v>
+        <v>133.4</v>
       </c>
       <c r="I59" t="n">
         <v>133.1818111893234</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.3</v>
+        <v>-6.34</v>
       </c>
       <c r="L59" t="n">
         <v>7.37</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.59</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45050</v>
+        <v>45051</v>
       </c>
       <c r="H60" t="n">
-        <v>139.4</v>
+        <v>127.75</v>
       </c>
       <c r="I60" t="n">
         <v>131.2486099373599</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>4.5</v>
+        <v>-4.24</v>
       </c>
       <c r="L60" t="n">
-        <v>0.97</v>
+        <v>4.8</v>
       </c>
       <c r="M60" t="n">
         <v>0.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0.78</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="O60" t="n">
         <v>0.98</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.99</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H61" t="n">
-        <v>126.15</v>
+        <v>127.55</v>
       </c>
       <c r="I61" t="n">
         <v>126.7736634901343</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K61" t="n">
-        <v>1.25</v>
+        <v>0.16</v>
       </c>
       <c r="L61" t="n">
         <v>9.82</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.02</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45119</v>
+        <v>45120</v>
       </c>
       <c r="H62" t="n">
-        <v>134.25</v>
+        <v>126.75</v>
       </c>
       <c r="I62" t="n">
         <v>127.3507133186574</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
-        <v>5.25</v>
+        <v>-0.63</v>
       </c>
       <c r="L62" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="M62" t="n">
         <v>0.23</v>
       </c>
       <c r="N62" t="n">
-        <v>0.92</v>
+        <v>5.59</v>
       </c>
       <c r="O62" t="n">
         <v>1.11</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>10.79</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45160</v>
+        <v>45161</v>
       </c>
       <c r="H63" t="n">
-        <v>136.05</v>
+        <v>141.7</v>
       </c>
       <c r="I63" t="n">
         <v>137.9864222118875</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.34</v>
+        <v>-11.79</v>
       </c>
       <c r="L63" t="n">
-        <v>9.859999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="M63" t="n">
         <v>1.73</v>
       </c>
       <c r="N63" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="O63" t="n">
         <v>-5.59</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.95</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H64" t="n">
-        <v>141.85</v>
+        <v>138.15</v>
       </c>
       <c r="I64" t="n">
         <v>139.8811850867026</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K64" t="n">
-        <v>0.11</v>
+        <v>-2.51</v>
       </c>
       <c r="L64" t="n">
         <v>4.16</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H65" t="n">
-        <v>149.45</v>
+        <v>152.9</v>
       </c>
       <c r="I65" t="n">
         <v>150.0967355270274</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.18</v>
+        <v>-10.68</v>
       </c>
       <c r="L65" t="n">
-        <v>8.9</v>
+        <v>11.15</v>
       </c>
       <c r="M65" t="n">
         <v>1.03</v>
       </c>
       <c r="N65" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="O65" t="n">
         <v>-2.61</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.14</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H66" t="n">
-        <v>149.7</v>
+        <v>145.9</v>
       </c>
       <c r="I66" t="n">
         <v>148.1056272621373</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.09</v>
+        <v>-4.58</v>
       </c>
       <c r="L66" t="n">
-        <v>5.1</v>
+        <v>5.92</v>
       </c>
       <c r="M66" t="n">
         <v>1.24</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.18</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45336</v>
+        <v>45337</v>
       </c>
       <c r="H67" t="n">
-        <v>149.45</v>
+        <v>156.6</v>
       </c>
       <c r="I67" t="n">
         <v>154.3166536089623</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.43</v>
+        <v>-7.33</v>
       </c>
       <c r="L67" t="n">
-        <v>3.77</v>
+        <v>7.75</v>
       </c>
       <c r="M67" t="n">
         <v>1.92</v>
       </c>
       <c r="N67" t="n">
-        <v>2.57</v>
+        <v>4.78</v>
       </c>
       <c r="O67" t="n">
         <v>-2.54</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.21</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H68" t="n">
-        <v>151.75</v>
+        <v>148.5</v>
       </c>
       <c r="I68" t="n">
         <v>150.2796461831434</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.1</v>
+        <v>-5.17</v>
       </c>
       <c r="L68" t="n">
-        <v>5.43</v>
+        <v>6.29</v>
       </c>
       <c r="M68" t="n">
         <v>6.11</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H69" t="n">
-        <v>155.8</v>
+        <v>159</v>
       </c>
       <c r="I69" t="n">
         <v>157.680066192839</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.92</v>
+        <v>-7.07</v>
       </c>
       <c r="L69" t="n">
-        <v>6.84</v>
+        <v>7.41</v>
       </c>
       <c r="M69" t="n">
         <v>1.46</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>8.84</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H70" t="n">
-        <v>164.35</v>
+        <v>154.65</v>
       </c>
       <c r="I70" t="n">
         <v>155.493152853085</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K70" t="n">
-        <v>3.36</v>
+        <v>-2.74</v>
       </c>
       <c r="L70" t="n">
-        <v>6.6</v>
+        <v>6.92</v>
       </c>
       <c r="M70" t="n">
         <v>1.28</v>
       </c>
       <c r="N70" t="n">
-        <v>2.41</v>
+        <v>5.9</v>
       </c>
       <c r="O70" t="n">
         <v>2.05</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>10.37</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H71" t="n">
-        <v>167.59</v>
+        <v>173.86</v>
       </c>
       <c r="I71" t="n">
         <v>170.6836624322235</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.369999999999999</v>
+        <v>-12.42</v>
       </c>
       <c r="L71" t="n">
-        <v>9.34</v>
+        <v>12.87</v>
       </c>
       <c r="M71" t="n">
         <v>0.99</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>11.39</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45538</v>
+        <v>45539</v>
       </c>
       <c r="H72" t="n">
-        <v>194.61</v>
+        <v>187.87</v>
       </c>
       <c r="I72" t="n">
         <v>191.0748465793625</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K72" t="n">
-        <v>11.93</v>
+        <v>8.06</v>
       </c>
       <c r="L72" t="n">
         <v>4.26</v>
@@ -4545,7 +5408,7 @@
         <v>4.72</v>
       </c>
       <c r="N72" t="n">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="O72" t="n">
         <v>3.74</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.18</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="H73" t="n">
-        <v>193.71</v>
+        <v>196.73</v>
       </c>
       <c r="I73" t="n">
         <v>195.134616219772</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.11</v>
+        <v>-4.72</v>
       </c>
       <c r="L73" t="n">
-        <v>4.06</v>
+        <v>5.23</v>
       </c>
       <c r="M73" t="n">
         <v>1.5</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.2</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H74" t="n">
-        <v>193.67</v>
+        <v>184.2</v>
       </c>
       <c r="I74" t="n">
         <v>185.3658816397495</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.56</v>
+        <v>-6.37</v>
       </c>
       <c r="L74" t="n">
-        <v>2.88</v>
+        <v>7.16</v>
       </c>
       <c r="M74" t="n">
         <v>1.94</v>
       </c>
       <c r="N74" t="n">
-        <v>1.68</v>
+        <v>4.89</v>
       </c>
       <c r="O74" t="n">
         <v>1.56</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>11.93</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="H75" t="n">
-        <v>200.7</v>
+        <v>203.24</v>
       </c>
       <c r="I75" t="n">
         <v>201.7130546554899</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.960000000000001</v>
+        <v>-10.34</v>
       </c>
       <c r="L75" t="n">
-        <v>9.35</v>
+        <v>11.18</v>
       </c>
       <c r="M75" t="n">
         <v>4.84</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>10.68</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="H76" t="n">
-        <v>210.29</v>
+        <v>200.03</v>
       </c>
       <c r="I76" t="n">
         <v>202.8211939329607</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K76" t="n">
-        <v>3.47</v>
+        <v>-1.58</v>
       </c>
       <c r="L76" t="n">
         <v>4.03</v>
@@ -4773,7 +5684,7 @@
         <v>0.74</v>
       </c>
       <c r="N76" t="n">
-        <v>3.81</v>
+        <v>4.88</v>
       </c>
       <c r="O76" t="n">
         <v>1.27</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>9.25</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H77" t="n">
-        <v>187.3</v>
+        <v>195.8</v>
       </c>
       <c r="I77" t="n">
         <v>189.3065180469914</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K77" t="n">
-        <v>6.36</v>
+        <v>2.11</v>
       </c>
       <c r="L77" t="n">
         <v>5.48</v>
@@ -4830,7 +5753,7 @@
         <v>1.01</v>
       </c>
       <c r="N77" t="n">
-        <v>3.34</v>
+        <v>4.54</v>
       </c>
       <c r="O77" t="n">
         <v>-4.88</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>8.84</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H78" t="n">
-        <v>191.51</v>
+        <v>187.29</v>
       </c>
       <c r="I78" t="n">
         <v>188.1209453098917</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.19</v>
+        <v>-4.35</v>
       </c>
       <c r="L78" t="n">
         <v>4.74</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.26</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="H79" t="n">
-        <v>201.17</v>
+        <v>203.43</v>
       </c>
       <c r="I79" t="n">
         <v>203.2464569824834</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.41</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>8.59</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M79" t="n">
         <v>1.93</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>7.67</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H80" t="n">
-        <v>204.68</v>
+        <v>202.43</v>
       </c>
       <c r="I80" t="n">
         <v>204.2569916273224</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K80" t="n">
-        <v>0.61</v>
+        <v>-0.49</v>
       </c>
       <c r="L80" t="n">
         <v>1.88</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>5.67</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H81" t="n">
-        <v>199.17</v>
+        <v>202.61</v>
       </c>
       <c r="I81" t="n">
         <v>199.6377651452285</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K81" t="n">
-        <v>1.61</v>
+        <v>-0.09</v>
       </c>
       <c r="L81" t="n">
         <v>1.14</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.81</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H82" t="n">
-        <v>263.75</v>
+        <v>256.7</v>
       </c>
       <c r="I82" t="n">
         <v>256.9474911169434</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K82" t="n">
-        <v>30.18</v>
+        <v>26.7</v>
       </c>
       <c r="L82" t="n">
         <v>1.61</v>
@@ -5115,7 +6098,7 @@
         <v>0.39</v>
       </c>
       <c r="N82" t="n">
-        <v>1.39</v>
+        <v>2.67</v>
       </c>
       <c r="O82" t="n">
         <v>1.73</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>7.13</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H83" t="n">
-        <v>246.85</v>
+        <v>270.25</v>
       </c>
       <c r="I83" t="n">
         <v>262.1482398860602</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K83" t="n">
-        <v>3.84</v>
+        <v>-5.28</v>
       </c>
       <c r="L83" t="n">
-        <v>3.23</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M83" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="N83" t="n">
-        <v>0.72</v>
+        <v>9.48</v>
       </c>
       <c r="O83" t="n">
         <v>-2.67</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>11.79</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H84" t="n">
-        <v>286.5</v>
+        <v>273.3</v>
       </c>
       <c r="I84" t="n">
         <v>280.315981668253</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K84" t="n">
-        <v>6.01</v>
+        <v>1.13</v>
       </c>
       <c r="L84" t="n">
         <v>8.44</v>
@@ -5229,7 +6236,7 @@
         <v>3.28</v>
       </c>
       <c r="N84" t="n">
-        <v>2.88</v>
+        <v>4.61</v>
       </c>
       <c r="O84" t="n">
         <v>9.48</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>9.44</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H85" t="n">
-        <v>283.3</v>
+        <v>291.7</v>
       </c>
       <c r="I85" t="n">
         <v>285.1411665757503</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K85" t="n">
-        <v>-3.66</v>
+        <v>-6.73</v>
       </c>
       <c r="L85" t="n">
-        <v>5.67</v>
+        <v>7.12</v>
       </c>
       <c r="M85" t="n">
         <v>4.07</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>10.94</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H86" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I86" t="n">
         <v>342.991180064913</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K86" t="n">
-        <v>17.59</v>
+        <v>17.24</v>
       </c>
       <c r="L86" t="n">
         <v>5.01</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>6</v>
+      </c>
+      <c r="U86" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -5379,28 +6422,28 @@
         <v>6.13</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="H87" t="n">
-        <v>338</v>
+        <v>348.85</v>
       </c>
       <c r="I87" t="n">
         <v>339.8556093320215</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K87" t="n">
-        <v>1.17</v>
+        <v>-2</v>
       </c>
       <c r="L87" t="n">
-        <v>1.48</v>
+        <v>3.95</v>
       </c>
       <c r="M87" t="n">
         <v>0.61</v>
       </c>
       <c r="N87" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="O87" t="n">
         <v>-0.29</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5460,6 +6515,14 @@
       <c r="Q88" t="n">
         <v>7</v>
       </c>
+      <c r="R88" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10418,7 +11481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.2</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="6">
@@ -10428,7 +11491,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="7">
@@ -10438,7 +11501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
@@ -10448,7 +11511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -10458,7 +11521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="10">
@@ -10468,7 +11531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -10508,7 +11571,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.96</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="15">
@@ -10518,7 +11581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.75</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="16">
@@ -10528,7 +11591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.18</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="17">
@@ -10538,7 +11601,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.54</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="18">
@@ -10548,7 +11611,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="19">
@@ -10558,7 +11621,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.19</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
@@ -10568,7 +11631,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.68</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="21">
@@ -10578,7 +11641,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.76</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="22">
@@ -10588,7 +11651,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -10598,7 +11661,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -10608,7 +11671,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="25">
@@ -10628,7 +11691,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.87</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="27">
@@ -10638,7 +11701,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.17</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="28">
@@ -10648,7 +11711,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
